--- a/data/satisfaction_detail/2026/1-8月/住宿团队.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/住宿团队.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.92</v>
+        <v>9.867914485165796</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.98</v>
+        <v>9.956710296684118</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.81</v>
+        <v>9.793001745200696</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.94</v>
+        <v>9.947015706806281</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.720837696335078</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98848167539267</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.75</v>
+        <v>9.655724258289704</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98041884816754</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.960741710296682</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9</v>
+        <v>8.774158031088083</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.422927461139897</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.951204188481675</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.99</v>
+        <v>9.990209424083769</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98130890052356</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>10</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.98</v>
+        <v>9.96544502617801</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -605,7 +605,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9.99</v>
+        <v>9.929834205933682</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.99</v>
+        <v>9.995549738219895</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.99</v>
+        <v>9.836823734729492</v>
       </c>
     </row>
     <row r="14">
@@ -657,7 +657,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.98</v>
+        <v>9.836823734729492</v>
       </c>
     </row>
     <row r="17">
@@ -670,7 +670,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.99</v>
+        <v>9.836823734729492</v>
       </c>
     </row>
     <row r="18">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.94</v>
+        <v>9.815846422338568</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10</v>
+        <v>9.988577661431064</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.959354275741712</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.98</v>
+        <v>9.977155322862128</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.618756371049949</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>10</v>
